--- a/output/roomself_excel/3817.xlsx
+++ b/output/roomself_excel/3817.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>144771</v>
+        <v>119064</v>
       </c>
       <c r="D2" t="n">
-        <v>3088</v>
+        <v>2860</v>
       </c>
       <c r="E2" t="n">
         <v>476</v>
       </c>
       <c r="F2" t="n">
-        <v>346</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>284050</v>
+        <v>223820</v>
       </c>
       <c r="D3" t="n">
-        <v>5624</v>
+        <v>3876</v>
       </c>
       <c r="E3" t="n">
-        <v>1254</v>
+        <v>614</v>
       </c>
       <c r="F3" t="n">
-        <v>829</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>49300</v>
+        <v>144771</v>
       </c>
       <c r="D4" t="n">
-        <v>1840</v>
+        <v>3088</v>
       </c>
       <c r="E4" t="n">
-        <v>170</v>
+        <v>476</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25330</v>
+        <v>49300</v>
       </c>
       <c r="D5" t="n">
-        <v>1276</v>
+        <v>1840</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>119064</v>
+        <v>25330</v>
       </c>
       <c r="D6" t="n">
-        <v>2860</v>
+        <v>1276</v>
       </c>
       <c r="E6" t="n">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>289</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>60230</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2204</v>
+      </c>
+      <c r="E7" t="n">
+        <v>399</v>
+      </c>
+      <c r="F7" t="n">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/3817.xlsx
+++ b/output/roomself_excel/3817.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2860</v>
       </c>
-      <c r="E2" t="n">
-        <v>476</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>289</v>
+        <v>264</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>451</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3876</v>
       </c>
-      <c r="E3" t="n">
-        <v>614</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>430</v>
+        <v>1001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>380</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>3088</v>
       </c>
-      <c r="E4" t="n">
-        <v>476</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>346</v>
+        <v>451</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>321</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +609,20 @@
       <c r="D5" t="n">
         <v>1840</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>170</v>
       </c>
-      <c r="F5" t="n">
-        <v>25</v>
-      </c>
+      <c r="G5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +639,12 @@
       <c r="D6" t="n">
         <v>1276</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +661,27 @@
       <c r="D7" t="n">
         <v>2204</v>
       </c>
-      <c r="E7" t="n">
-        <v>399</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>177</v>
+        <v>374</v>
+      </c>
+      <c r="G7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>152</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
